--- a/exports/trend_1d/GODFRYPHLP_full_report.xlsx
+++ b/exports/trend_1d/GODFRYPHLP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.26</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42040</v>
+        <v>42041</v>
       </c>
       <c r="H2" t="n">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="I2" t="n">
         <v>183.324415801392</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>3.74</v>
+        <v>-6.95</v>
       </c>
       <c r="L2" t="n">
-        <v>5.35</v>
+        <v>8.56</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>3.61</v>
       </c>
       <c r="N2" t="n">
-        <v>1.6</v>
+        <v>10.31</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>15.32</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42103</v>
+        <v>42104</v>
       </c>
       <c r="H3" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I3" t="n">
         <v>156.31834098399</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K3" t="n">
-        <v>11.49</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>7.47</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.07</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42160</v>
+        <v>42163</v>
       </c>
       <c r="H4" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I4" t="n">
         <v>157.2034573625324</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.63</v>
+        <v>-1.26</v>
       </c>
       <c r="L4" t="n">
         <v>5.03</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.64</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42188</v>
+        <v>42191</v>
       </c>
       <c r="H5" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="I5" t="n">
         <v>166.6039980337929</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.64</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>11.46</v>
@@ -726,7 +785,7 @@
         <v>1.95</v>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>-0.63</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>16.52</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42355</v>
+        <v>42356</v>
       </c>
       <c r="H6" t="n">
-        <v>445</v>
+        <v>401</v>
       </c>
       <c r="I6" t="n">
         <v>430.7210576432254</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K6" t="n">
-        <v>158.72</v>
+        <v>133.14</v>
       </c>
       <c r="L6" t="n">
         <v>8.720000000000001</v>
@@ -783,7 +854,7 @@
         <v>5.88</v>
       </c>
       <c r="N6" t="n">
-        <v>8.609999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>8.859999999999999</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>31.46</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42472</v>
+        <v>42473</v>
       </c>
       <c r="H7" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I7" t="n">
         <v>404.0873096981468</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5</v>
+        <v>-1.75</v>
       </c>
       <c r="L7" t="n">
         <v>21.2</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.74</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42485</v>
+        <v>42486</v>
       </c>
       <c r="H8" t="n">
-        <v>376</v>
+        <v>310</v>
       </c>
       <c r="I8" t="n">
         <v>364.1893201800654</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.84</v>
+        <v>-24.02</v>
       </c>
       <c r="L8" t="n">
-        <v>8.33</v>
+        <v>25</v>
       </c>
       <c r="M8" t="n">
-        <v>-0</v>
+        <v>7.98</v>
       </c>
       <c r="N8" t="n">
-        <v>3.09</v>
+        <v>17.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.24</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>25.7</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42556</v>
+        <v>42558</v>
       </c>
       <c r="H9" t="n">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="I9" t="n">
         <v>300.9676403641278</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K9" t="n">
-        <v>3.23</v>
+        <v>0.32</v>
       </c>
       <c r="L9" t="n">
         <v>11.61</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.91</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42634</v>
+        <v>42635</v>
       </c>
       <c r="H10" t="n">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="I10" t="n">
         <v>436.1614122222418</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K10" t="n">
-        <v>42.07</v>
+        <v>39.81</v>
       </c>
       <c r="L10" t="n">
         <v>3.56</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>15.66</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42657</v>
+        <v>42660</v>
       </c>
       <c r="H11" t="n">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="I11" t="n">
         <v>476.0514585103355</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.56</v>
+        <v>-15.05</v>
       </c>
       <c r="L11" t="n">
-        <v>11.34</v>
+        <v>17.13</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.71</v>
       </c>
       <c r="N11" t="n">
-        <v>5.67</v>
+        <v>5.97</v>
       </c>
       <c r="O11" t="n">
         <v>-1.59</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>15.79</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42682</v>
+        <v>42683</v>
       </c>
       <c r="H12" t="n">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="I12" t="n">
         <v>429.9323966397477</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.859999999999999</v>
+        <v>-14.29</v>
       </c>
       <c r="L12" t="n">
-        <v>10.66</v>
+        <v>27.97</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>7.81</v>
       </c>
       <c r="N12" t="n">
-        <v>3.76</v>
+        <v>4.91</v>
       </c>
       <c r="O12" t="n">
         <v>5.97</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.84</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42730</v>
+        <v>42731</v>
       </c>
       <c r="H13" t="n">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="I13" t="n">
         <v>310.8091551013305</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K13" t="n">
-        <v>34.74</v>
+        <v>21.83</v>
       </c>
       <c r="L13" t="n">
         <v>3.99</v>
@@ -1182,7 +1337,7 @@
         <v>3.29</v>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>19.78</v>
       </c>
       <c r="O13" t="n">
         <v>-4.91</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>21.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42818</v>
+        <v>42821</v>
       </c>
       <c r="H14" t="n">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="I14" t="n">
         <v>387.7355355330914</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K14" t="n">
-        <v>17.72</v>
+        <v>12.01</v>
       </c>
       <c r="L14" t="n">
         <v>16.82</v>
@@ -1239,7 +1406,7 @@
         <v>2.27</v>
       </c>
       <c r="N14" t="n">
-        <v>4.15</v>
+        <v>4.85</v>
       </c>
       <c r="O14" t="n">
         <v>19.78</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>16.53</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42851</v>
+        <v>42852</v>
       </c>
       <c r="H15" t="n">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="I15" t="n">
         <v>403.2565800352284</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.17</v>
+        <v>-9.92</v>
       </c>
       <c r="L15" t="n">
         <v>11.53</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>14.71</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42933</v>
+        <v>42934</v>
       </c>
       <c r="H16" t="n">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="I16" t="n">
         <v>387.7230961405915</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.24</v>
+        <v>-5.85</v>
       </c>
       <c r="L16" t="n">
-        <v>6.1</v>
+        <v>10.49</v>
       </c>
       <c r="M16" t="n">
-        <v>2.33</v>
+        <v>10.02</v>
       </c>
       <c r="N16" t="n">
-        <v>4.37</v>
+        <v>5.62</v>
       </c>
       <c r="O16" t="n">
         <v>3.54</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.69</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42961</v>
+        <v>42963</v>
       </c>
       <c r="H17" t="n">
-        <v>303</v>
+        <v>347</v>
       </c>
       <c r="I17" t="n">
         <v>341.9151220087253</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>21.5</v>
+        <v>10.1</v>
       </c>
       <c r="L17" t="n">
         <v>3.89</v>
@@ -1410,7 +1613,7 @@
         <v>3.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.57</v>
+        <v>14.52</v>
       </c>
       <c r="O17" t="n">
         <v>-5.62</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>23.89</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H18" t="n">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="I18" t="n">
         <v>324.1129929803454</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.31</v>
+        <v>-7.2</v>
       </c>
       <c r="L18" t="n">
         <v>14.12</v>
@@ -1467,7 +1682,7 @@
         <v>1.67</v>
       </c>
       <c r="N18" t="n">
-        <v>2.02</v>
+        <v>5.01</v>
       </c>
       <c r="O18" t="n">
         <v>14.52</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12.93</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43110</v>
+        <v>43111</v>
       </c>
       <c r="H19" t="n">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="I19" t="n">
         <v>348.8283302752228</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.14</v>
+        <v>-10.56</v>
       </c>
       <c r="L19" t="n">
         <v>11.49</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.32</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43125</v>
+        <v>43129</v>
       </c>
       <c r="H20" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I20" t="n">
         <v>320.0726843671115</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.83</v>
+        <v>-10.11</v>
       </c>
       <c r="L20" t="n">
         <v>10.39</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43173</v>
+        <v>43174</v>
       </c>
       <c r="H21" t="n">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="I21" t="n">
         <v>298.4473201593673</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K21" t="n">
-        <v>9.69</v>
+        <v>5.62</v>
       </c>
       <c r="L21" t="n">
         <v>2.5</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H22" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I22" t="n">
         <v>275.3706949484131</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.609999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="L22" t="n">
         <v>13.25</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H23" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="I23" t="n">
         <v>255.9394461473362</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K23" t="n">
-        <v>8.789999999999999</v>
+        <v>5.13</v>
       </c>
       <c r="L23" t="n">
         <v>1.83</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>13.55</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H24" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="I24" t="n">
         <v>285.9534003060824</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K24" t="n">
-        <v>15.83</v>
+        <v>6.18</v>
       </c>
       <c r="L24" t="n">
         <v>4.25</v>
@@ -1809,7 +2096,7 @@
         <v>1.38</v>
       </c>
       <c r="N24" t="n">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
       <c r="O24" t="n">
         <v>4.02</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>21.89</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43410</v>
+        <v>43413</v>
       </c>
       <c r="H25" t="n">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="I25" t="n">
         <v>273.5306364319039</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K25" t="n">
-        <v>5.82</v>
+        <v>-3.27</v>
       </c>
       <c r="L25" t="n">
         <v>12</v>
@@ -1866,7 +2165,7 @@
         <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>6.17</v>
+        <v>9.65</v>
       </c>
       <c r="O25" t="n">
         <v>-8.33</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>17.97</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43508</v>
+        <v>43509</v>
       </c>
       <c r="H26" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I26" t="n">
         <v>289.4633947462105</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K26" t="n">
-        <v>2.46</v>
+        <v>1.76</v>
       </c>
       <c r="L26" t="n">
         <v>9.859999999999999</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.9</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H27" t="n">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="I27" t="n">
         <v>319.1511086890196</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K27" t="n">
-        <v>-9</v>
+        <v>-19.03</v>
       </c>
       <c r="L27" t="n">
-        <v>12.46</v>
+        <v>20.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.88</v>
       </c>
       <c r="N27" t="n">
-        <v>5.63</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-0.6899999999999999</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>16.07</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43585</v>
+        <v>43587</v>
       </c>
       <c r="H28" t="n">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="I28" t="n">
         <v>361.1391445391239</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K28" t="n">
-        <v>6.98</v>
+        <v>4.36</v>
       </c>
       <c r="L28" t="n">
         <v>8.720000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.89</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43686</v>
+        <v>43690</v>
       </c>
       <c r="H29" t="n">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="I29" t="n">
         <v>251.9859725725157</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K29" t="n">
-        <v>34.26</v>
+        <v>20.89</v>
       </c>
       <c r="L29" t="n">
         <v>3.06</v>
       </c>
       <c r="M29" t="n">
-        <v>4.41</v>
+        <v>11.44</v>
       </c>
       <c r="N29" t="n">
-        <v>4.12</v>
+        <v>20.34</v>
       </c>
       <c r="O29" t="n">
         <v>-2.45</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>18.52</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43858</v>
+        <v>43859</v>
       </c>
       <c r="H30" t="n">
-        <v>458</v>
+        <v>416</v>
       </c>
       <c r="I30" t="n">
         <v>429.179631564952</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K30" t="n">
-        <v>61.27</v>
+        <v>46.48</v>
       </c>
       <c r="L30" t="n">
         <v>10.56</v>
@@ -2151,7 +2510,7 @@
         <v>2.63</v>
       </c>
       <c r="N30" t="n">
-        <v>6.37</v>
+        <v>9.17</v>
       </c>
       <c r="O30" t="n">
         <v>20.34</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>23.13</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43868</v>
+        <v>43871</v>
       </c>
       <c r="H31" t="n">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="I31" t="n">
         <v>450.6917231644817</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.16</v>
+        <v>-8.41</v>
       </c>
       <c r="L31" t="n">
         <v>12.02</v>
       </c>
       <c r="M31" t="n">
-        <v>1.02</v>
+        <v>2.82</v>
       </c>
       <c r="N31" t="n">
         <v>11.73</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>18.92</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43887</v>
+        <v>43888</v>
       </c>
       <c r="H32" t="n">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="I32" t="n">
         <v>394.1386141463638</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K32" t="n">
-        <v>-12.2</v>
+        <v>-14.41</v>
       </c>
       <c r="L32" t="n">
-        <v>12.64</v>
+        <v>17.07</v>
       </c>
       <c r="M32" t="n">
         <v>0.98</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>19.62</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43943</v>
+        <v>43944</v>
       </c>
       <c r="H33" t="n">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="I33" t="n">
         <v>351.4200967792823</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K33" t="n">
-        <v>10.1</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L33" t="n">
         <v>5.96</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>22.94</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44034</v>
+        <v>44035</v>
       </c>
       <c r="H34" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I34" t="n">
         <v>308.8723439918318</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K34" t="n">
-        <v>-12.15</v>
+        <v>-12.99</v>
       </c>
       <c r="L34" t="n">
         <v>13.28</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>7.9</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44069</v>
+        <v>44070</v>
       </c>
       <c r="H35" t="n">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="I35" t="n">
         <v>326.1089322540035</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.9</v>
+        <v>-12.01</v>
       </c>
       <c r="L35" t="n">
-        <v>7.14</v>
+        <v>18.18</v>
       </c>
       <c r="M35" t="n">
-        <v>2.24</v>
+        <v>10.94</v>
       </c>
       <c r="N35" t="n">
-        <v>2.94</v>
+        <v>7.81</v>
       </c>
       <c r="O35" t="n">
         <v>-0.96</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44078</v>
+        <v>44081</v>
       </c>
       <c r="H36" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I36" t="n">
         <v>312.9734091949128</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.279999999999999</v>
+        <v>-10.72</v>
       </c>
       <c r="L36" t="n">
-        <v>9.859999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="M36" t="n">
         <v>1.16</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>13.3</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44158</v>
+        <v>44159</v>
       </c>
       <c r="H37" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I37" t="n">
         <v>311.5072386515764</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="L37" t="n">
-        <v>4.22</v>
+        <v>4.55</v>
       </c>
       <c r="M37" t="n">
         <v>1.41</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44186</v>
+        <v>44187</v>
       </c>
       <c r="H38" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I38" t="n">
         <v>307.2210445702301</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.64</v>
+        <v>-1.6</v>
       </c>
       <c r="L38" t="n">
         <v>4.17</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.7</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H39" t="n">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="I39" t="n">
         <v>300.5601506561919</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K39" t="n">
-        <v>4.23</v>
+        <v>1.3</v>
       </c>
       <c r="L39" t="n">
         <v>11.4</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>6.69</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44418</v>
+        <v>44419</v>
       </c>
       <c r="H40" t="n">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I40" t="n">
         <v>328.7925682584831</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K40" t="n">
-        <v>10.23</v>
+        <v>8.25</v>
       </c>
       <c r="L40" t="n">
         <v>2.97</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.57</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H41" t="n">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="I41" t="n">
         <v>342.5084407177912</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.13</v>
+        <v>-6.71</v>
       </c>
       <c r="L41" t="n">
-        <v>9.15</v>
+        <v>11.59</v>
       </c>
       <c r="M41" t="n">
         <v>1.23</v>
       </c>
       <c r="N41" t="n">
-        <v>3.25</v>
+        <v>4.48</v>
       </c>
       <c r="O41" t="n">
         <v>-1.8</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.75</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H42" t="n">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="I42" t="n">
         <v>391.1424624590271</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K42" t="n">
-        <v>13.14</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>4.29</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>15.63</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44532</v>
+        <v>44533</v>
       </c>
       <c r="H43" t="n">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="I43" t="n">
         <v>431.5668047463449</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>-12.4</v>
+        <v>-15.83</v>
       </c>
       <c r="L43" t="n">
-        <v>13.46</v>
+        <v>20.05</v>
       </c>
       <c r="M43" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="N43" t="n">
         <v>4.16</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>12.17</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44550</v>
+        <v>44551</v>
       </c>
       <c r="H44" t="n">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="I44" t="n">
         <v>385.5664692072261</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>-11.39</v>
+        <v>-13.44</v>
       </c>
       <c r="L44" t="n">
-        <v>12.07</v>
+        <v>14.12</v>
       </c>
       <c r="M44" t="n">
         <v>1</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>14.01</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44643</v>
+        <v>44644</v>
       </c>
       <c r="H45" t="n">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="I45" t="n">
         <v>364.3230153862611</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K45" t="n">
-        <v>5.53</v>
+        <v>3.95</v>
       </c>
       <c r="L45" t="n">
         <v>4.74</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.71</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H46" t="n">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="I46" t="n">
         <v>381.2922885595261</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="n">
-        <v>9.039999999999999</v>
+        <v>3.01</v>
       </c>
       <c r="L46" t="n">
         <v>8.220000000000001</v>
@@ -3063,7 +3614,7 @@
         <v>1.55</v>
       </c>
       <c r="N46" t="n">
-        <v>4.53</v>
+        <v>5.53</v>
       </c>
       <c r="O46" t="n">
         <v>1.67</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>20.43</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44771</v>
+        <v>44774</v>
       </c>
       <c r="H47" t="n">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="I47" t="n">
         <v>388.2195333959006</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.06</v>
+        <v>-5.05</v>
       </c>
       <c r="L47" t="n">
         <v>13.03</v>
       </c>
       <c r="M47" t="n">
-        <v>3.46</v>
+        <v>5.79</v>
       </c>
       <c r="N47" t="n">
         <v>5.77</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.01</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44805</v>
+        <v>44806</v>
       </c>
       <c r="H48" t="n">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="I48" t="n">
         <v>367.7705769443327</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.84</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>7.34</v>
+        <v>10.13</v>
       </c>
       <c r="M48" t="n">
         <v>0.53</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>10.47</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44816</v>
+        <v>44817</v>
       </c>
       <c r="H49" t="n">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="I49" t="n">
         <v>387.0772272287556</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.59</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>6.7</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M49" t="n">
         <v>1.62</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.64</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H50" t="n">
-        <v>606</v>
+        <v>556</v>
       </c>
       <c r="I50" t="n">
         <v>595.7542037227862</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K50" t="n">
-        <v>54.99</v>
+        <v>42.2</v>
       </c>
       <c r="L50" t="n">
         <v>7.93</v>
@@ -3291,7 +3890,7 @@
         <v>1.79</v>
       </c>
       <c r="N50" t="n">
-        <v>6.48</v>
+        <v>8.25</v>
       </c>
       <c r="O50" t="n">
         <v>3.44</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>24.13</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44932</v>
+        <v>44935</v>
       </c>
       <c r="H51" t="n">
-        <v>666</v>
+        <v>709</v>
       </c>
       <c r="I51" t="n">
         <v>690.1893418199126</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>-19.78</v>
+        <v>-27.52</v>
       </c>
       <c r="L51" t="n">
-        <v>22.12</v>
+        <v>28.78</v>
       </c>
       <c r="M51" t="n">
         <v>1.83</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>16.87</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44960</v>
+        <v>44963</v>
       </c>
       <c r="H52" t="n">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="I52" t="n">
         <v>602.5467291930626</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.39</v>
+        <v>-15.23</v>
       </c>
       <c r="L52" t="n">
         <v>16.36</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>15.94</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44988</v>
+        <v>44991</v>
       </c>
       <c r="H53" t="n">
-        <v>630</v>
+        <v>666</v>
       </c>
       <c r="I53" t="n">
         <v>637.1541023740403</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.83</v>
+        <v>-10.82</v>
       </c>
       <c r="L53" t="n">
-        <v>5.32</v>
+        <v>11.48</v>
       </c>
       <c r="M53" t="n">
         <v>1.02</v>
       </c>
       <c r="N53" t="n">
-        <v>5.38</v>
+        <v>5.71</v>
       </c>
       <c r="O53" t="n">
         <v>-0.99</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>13.29</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H54" t="n">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="I54" t="n">
         <v>590.1232103622139</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.859999999999999</v>
+        <v>-11.56</v>
       </c>
       <c r="L54" t="n">
         <v>12.46</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>13.45</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45133</v>
+        <v>45134</v>
       </c>
       <c r="H55" t="n">
-        <v>575</v>
+        <v>636</v>
       </c>
       <c r="I55" t="n">
         <v>578.6961100361984</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K55" t="n">
-        <v>2.38</v>
+        <v>-7.98</v>
       </c>
       <c r="L55" t="n">
-        <v>3.57</v>
+        <v>11.71</v>
       </c>
       <c r="M55" t="n">
-        <v>2.03</v>
+        <v>14.43</v>
       </c>
       <c r="N55" t="n">
-        <v>3.36</v>
+        <v>10.61</v>
       </c>
       <c r="O55" t="n">
         <v>-2.97</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="H56" t="n">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="I56" t="n">
         <v>685.6378810092821</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K56" t="n">
-        <v>8.33</v>
+        <v>6.6</v>
       </c>
       <c r="L56" t="n">
         <v>1.42</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>9.19</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45293</v>
+        <v>45294</v>
       </c>
       <c r="H57" t="n">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="I57" t="n">
         <v>723.8620104416393</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.9</v>
+        <v>-7.23</v>
       </c>
       <c r="L57" t="n">
-        <v>8.109999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="N57" t="n">
         <v>2.87</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.78</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H58" t="n">
-        <v>1082</v>
+        <v>978</v>
       </c>
       <c r="I58" t="n">
         <v>1005.142982586116</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K58" t="n">
-        <v>48.83</v>
+        <v>34.53</v>
       </c>
       <c r="L58" t="n">
         <v>5.36</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>26.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45406</v>
+        <v>45407</v>
       </c>
       <c r="H59" t="n">
-        <v>1044</v>
+        <v>1150</v>
       </c>
       <c r="I59" t="n">
         <v>1141.516314675427</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.75</v>
+        <v>-17.59</v>
       </c>
       <c r="L59" t="n">
-        <v>15.44</v>
+        <v>18.92</v>
       </c>
       <c r="M59" t="n">
         <v>1.5</v>
       </c>
       <c r="N59" t="n">
-        <v>8.130000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="O59" t="n">
         <v>-9.609999999999999</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>16.35</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H60" t="n">
-        <v>2209</v>
+        <v>2136</v>
       </c>
       <c r="I60" t="n">
         <v>2163.723220934875</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K60" t="n">
-        <v>92.09</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="L60" t="n">
         <v>9.390000000000001</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>18.15</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H61" t="n">
-        <v>1506</v>
+        <v>1662</v>
       </c>
       <c r="I61" t="n">
         <v>1627.126596846919</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K61" t="n">
-        <v>29.49</v>
+        <v>22.19</v>
       </c>
       <c r="L61" t="n">
         <v>15.64</v>
@@ -3918,7 +4649,7 @@
         <v>2.56</v>
       </c>
       <c r="N61" t="n">
-        <v>8.890000000000001</v>
+        <v>10.36</v>
       </c>
       <c r="O61" t="n">
         <v>-3.3</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>19.09</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45716</v>
+        <v>45719</v>
       </c>
       <c r="H62" t="n">
-        <v>1730</v>
+        <v>1700</v>
       </c>
       <c r="I62" t="n">
         <v>1719.509594659788</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K62" t="n">
-        <v>4.09</v>
+        <v>2.29</v>
       </c>
       <c r="L62" t="n">
         <v>10.77</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>32.23</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45742</v>
+        <v>45743</v>
       </c>
       <c r="H63" t="n">
-        <v>2052</v>
+        <v>2155</v>
       </c>
       <c r="I63" t="n">
         <v>2123.468426355998</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>-20.71</v>
+        <v>-26.76</v>
       </c>
       <c r="L63" t="n">
-        <v>25.76</v>
+        <v>26.76</v>
       </c>
       <c r="M63" t="n">
         <v>1.69</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>17.09</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45828</v>
+        <v>45831</v>
       </c>
       <c r="H64" t="n">
-        <v>2670</v>
+        <v>2660</v>
       </c>
       <c r="I64" t="n">
         <v>2661.358032361357</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K64" t="n">
-        <v>23.9</v>
+        <v>23.43</v>
       </c>
       <c r="L64" t="n">
         <v>5.94</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>10.95</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="H65" t="n">
-        <v>2867</v>
+        <v>3014</v>
       </c>
       <c r="I65" t="n">
         <v>2951.343296121648</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.78</v>
+        <v>-13.31</v>
       </c>
       <c r="L65" t="n">
-        <v>9.44</v>
+        <v>18.57</v>
       </c>
       <c r="M65" t="n">
         <v>1.28</v>
       </c>
       <c r="N65" t="n">
-        <v>3.88</v>
+        <v>5.13</v>
       </c>
       <c r="O65" t="n">
         <v>-0.37</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>11.57</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H66" t="n">
-        <v>3108.4</v>
+        <v>3020.3</v>
       </c>
       <c r="I66" t="n">
         <v>3058.628951356065</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K66" t="n">
-        <v>3.13</v>
+        <v>0.21</v>
       </c>
       <c r="L66" t="n">
         <v>9.99</v>
       </c>
       <c r="M66" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="N66" t="n">
         <v>7.88</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>12.1</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H67" t="n">
-        <v>2184.6</v>
+        <v>2192.2</v>
       </c>
       <c r="I67" t="n">
         <v>2189.210242802076</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K67" t="n">
-        <v>27.67</v>
+        <v>27.42</v>
       </c>
       <c r="L67" t="n">
         <v>3.3</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>13.13</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="H68" t="n">
-        <v>2213.1</v>
+        <v>2148</v>
       </c>
       <c r="I68" t="n">
         <v>2178.358415386401</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>0.95</v>
+        <v>-2.02</v>
       </c>
       <c r="L68" t="n">
         <v>8.31</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>21.54</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H69" t="n">
-        <v>2124.9</v>
+        <v>2207.7</v>
       </c>
       <c r="I69" t="n">
         <v>2130.437419928174</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K69" t="n">
-        <v>1.08</v>
+        <v>-2.78</v>
       </c>
       <c r="L69" t="n">
-        <v>4.24</v>
+        <v>5.54</v>
       </c>
       <c r="M69" t="n">
         <v>4.51</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>12.29</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="H70" t="n">
-        <v>2170.1</v>
+        <v>2143</v>
       </c>
       <c r="I70" t="n">
         <v>2151.09115520655</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.7</v>
+        <v>-2.93</v>
       </c>
       <c r="L70" t="n">
         <v>5.74</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,25 +5318,25 @@
         <v>8.35</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="H71" t="n">
-        <v>2129.6</v>
+        <v>2210.5</v>
       </c>
       <c r="I71" t="n">
         <v>2202.169419785259</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K71" t="n">
-        <v>0.63</v>
+        <v>-3.15</v>
       </c>
       <c r="L71" t="n">
-        <v>1.48</v>
+        <v>4.91</v>
       </c>
       <c r="M71" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="N71" t="n">
         <v>4.06</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H72" t="n">
-        <v>2078.3</v>
+        <v>2025.4</v>
       </c>
       <c r="I72" t="n">
         <v>2061.867900545791</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.98</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L72" t="n">
         <v>8.93</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>38</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.1</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.5</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -9623,7 +10506,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -9633,7 +10516,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9643,7 +10526,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.2</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="14">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.61</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12.63</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.45</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>158.72</v>
+        <v>133.14</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.029999999999999</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.720000000000001</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="21">
@@ -9723,7 +10606,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.76</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="22">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="25">
@@ -9763,7 +10646,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.62</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="26">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.67</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="27">
@@ -9783,7 +10666,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.45</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="28">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
